--- a/my_agent/Landing/CTRL0037345.xlsx
+++ b/my_agent/Landing/CTRL0037345.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gautam.Bhattacharya\OneDrive - EY\Desktop\control flow\astra zeneca latest\CTRL0037345_v3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ajinkya\Desktop\Projects\lang-graph-poc\my_app\my_agent\Landing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BA6162B-9149-4D50-B217-53BE69155995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44D0B6D-D317-4004-A3DB-3E568BD6B704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B1EB8B7C-E22C-4E54-BB69-28FC8EA3B416}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" xr2:uid="{B1EB8B7C-E22C-4E54-BB69-28FC8EA3B416}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,8 +32,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -68,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="51">
   <si>
     <t>control_number</t>
   </si>
@@ -168,33 +166,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>In 37345_IPE4.jpg, check if the fields in the screenshot are filled correctly. The values in these fields should be as follows:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-1) G/L Account: 23020100
-2) Company Code: UK10
-3) Posting Date: 01.01.2024 to 31.03.2024
-%
-Validate the input parameters for GL 23020100
-%</t>
-    </r>
-  </si>
-  <si>
     <t>IPE3 GL 23040100_totals</t>
   </si>
   <si>
@@ -202,20 +173,6 @@
   </si>
   <si>
     <t>IPE1 GL 23040100_1</t>
-  </si>
-  <si>
-    <t>IPE4 GL 23020100</t>
-  </si>
-  <si>
-    <t>IPE5 GL 23020100_totals</t>
-  </si>
-  <si>
-    <t>Compare 37345_IPE5.xlsx with  37345_IPE5.jpg. 
-1. retrieve the Sum of column "Amount in local currency" from the excel
-2. retrieve the total value of column 'Amount in local cur' present at the bottom yellow panel in the screenshot. 
-%
-Validate the completeness and accuracy of GL 23020100 extract from SAP.
-%</t>
   </si>
   <si>
     <r>
@@ -1139,20 +1096,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0262C7-6BA8-46AB-B72D-B06AC8D7E1D4}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5" customWidth="1"/>
     <col min="5" max="5" width="58.33203125" customWidth="1"/>
     <col min="6" max="6" width="16.83203125" customWidth="1"/>
     <col min="11" max="11" width="39.1640625" customWidth="1"/>
     <col min="12" max="12" width="39.6640625" customWidth="1"/>
     <col min="13" max="13" width="61.33203125" customWidth="1"/>
-    <col min="14" max="14" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1184,22 +1140,16 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1231,19 +1181,13 @@
         <v>19</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>20</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1291,49 +1235,49 @@
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>34</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="S1" s="9" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>16</v>
@@ -1342,37 +1286,37 @@
         <v>17</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="N2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="O2" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="P2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="Q2" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="R2" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="S2" s="12" t="s">
         <v>50</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
